--- a/test_codes/enhanced_table_analyzer/output/514001_152_aligned.xlsx
+++ b/test_codes/enhanced_table_analyzer/output/514001_152_aligned.xlsx
@@ -11,11 +11,10 @@
     <sheet name="P152_表格_1_原始OCR" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="P152_表格_1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="P152_表格_2_原始OCR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="P152_表格_2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="P152_表格_3_原始OCR" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="P152_表格_3" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="P152_表格_4_原始OCR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="P152_表格_4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="P152_表格_3_原始OCR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="P152_表格_3" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="P152_表格_4_原始OCR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="P152_表格_4" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -539,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>成功匹配: 4 个</t>
+          <t>成功匹配: 3 个</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr"/>
@@ -557,7 +556,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>未匹配LLM表格: 0 个</t>
+          <t>未匹配LLM表格: 1 个</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr"/>
@@ -716,11 +715,11 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>表格_2</t>
+          <t>表格_3</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -740,16 +739,16 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -758,17 +757,17 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>H2×V0 D8×4</t>
+          <t>H2×V0 D8×5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>表格_3</t>
+          <t>表格_4</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -788,7 +787,7 @@
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0</v>
@@ -797,7 +796,7 @@
         <v>69</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -805,54 +804,6 @@
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>H2×V0 D8×5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>表格_4</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>人民币</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>H2×V0 D1×8</t>
         </is>
@@ -1145,275 +1096,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>法人股东名称</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>2023年12月31日</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>2023年12月31日</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>2022年12月31日</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>2022年12月31日</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>法人股东名称</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>持股金额</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>持股比例</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>持股金额</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>持股比例</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>浙江卫星控股股份有限公司</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>4,722.88</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>5.98%</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>3,937.20</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>5.23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>中法控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>4,134.06</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>5.23%</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>3,937.20</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>5.23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>浙江聚优非织造材料科技有限公司</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2,128.45</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>2.69%</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2,027.10</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2.69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>嘉兴农昕贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2,110.71</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>2.67%</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>2,010.20</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>嘉兴洁琪污水管网有限公司</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>1,773.77</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>2.24%</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>1,689.30</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2.24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>浙江荣祥纺织股份有限公司</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>1,185.26</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>1,128.82</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>梦迪集团有限公司</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>1,177.63</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>1.49%</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>浙江鸣春纺织股份有限公司</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>649.35</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>0.82%</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>618.42</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>0.82%</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>无OCR原始数据</t>
         </is>
       </c>
     </row>
@@ -1423,262 +1112,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>法人股东名称</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>2023年12月31日持股金额</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>2023年12月31日持股比例</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>2022年12月31日持股金额</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>2022年12月31日持股比例</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>浙江卫星控股股份有限公司</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>4,722.88</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>5.98%</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>3,937.20</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>5.23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>中法控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>4,134.06</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>5.23%</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>3,937.20</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>5.23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>浙江聚优非织造材料科技有限公司</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2,128.45</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2.69%</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>2,027.10</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2.69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>嘉兴农昕贸易有限公司</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2,110.71</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>2.67%</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2,010.20</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>嘉兴洁琪污水管网有限公司</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>1,773.77</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>2.24%</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1,689.30</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2.24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>浙江荣祥纺织股份有限公司</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>1,185.26</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>1,128.82</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>1.50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>梦迪集团有限公司</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>1,177.63</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>1.49%</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>浙江鸣春纺织股份有限公司</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>649.35</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>0.82%</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>618.42</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>0.82%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2000,7 +1433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2290,7 +1723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2444,7 +1877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
